--- a/data/Asset_Inventory.xlsx
+++ b/data/Asset_Inventory.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kate\OneDrive\Documents\GRC_Risk_Assessment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kate\OneDrive\Documents\GRC_Risk_Assessment\C3-GRC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F99973-BC35-4E88-8B9E-E6847439FF46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB7E476-74A6-4976-A844-C2B6F9A4C552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asset Inventory" sheetId="3" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Asset Inventory'!$A$1:$AI$43</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -41557,6 +41560,7 @@
       <c r="AI1002" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AI43" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="R2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="R3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/data/Asset_Inventory.xlsx
+++ b/data/Asset_Inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kate\OneDrive\Documents\GRC_Risk_Assessment\C3-GRC\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB7E476-74A6-4976-A844-C2B6F9A4C552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E134747C-BB92-4FCF-99A1-B826214185A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asset Inventory" sheetId="3" r:id="rId1"/>
@@ -1727,7 +1727,7 @@
     <col min="34" max="34" width="31.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>31</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="22.8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="34.200000000000003" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>20</v>
       </c>
